--- a/public/templates/forms/A-058-LogRetentionSchedule-FORM.xlsx
+++ b/public/templates/forms/A-058-LogRetentionSchedule-FORM.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
@@ -526,7 +526,7 @@
     <row r="2" ht="29.75" customHeight="1">
       <c r="A2" s="8" t="n"/>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Authority</t>
@@ -628,14 +628,14 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="29.75" customHeight="1">
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>« Replace the corner, column headers, and row labels with the dimensions this matrix maps (e.g., role × system, control × artifact). Add rows and columns as needed. »</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Log source \ Retention attribute</t>
@@ -662,7 +662,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="34.7" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>[CAD event / transaction logs]</t>
@@ -689,7 +689,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="34.7" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>[Call-handling / telephony (CPE) logs]</t>
@@ -716,7 +716,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="34.7" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
           <t>[Firewall / network / VPN logs]</t>
@@ -743,7 +743,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="21" ht="34.7" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>[Server / endpoint / EDR logs]</t>
@@ -770,7 +770,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="34.7" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t>[Physical access / badge &amp; video]</t>
@@ -797,7 +797,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" ht="34.7" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>[IDACS / CJIS access logs]</t>
@@ -954,7 +954,7 @@
       </c>
       <c r="E42" s="14" t="n"/>
     </row>
-    <row r="44" ht="80" customHeight="1">
+    <row r="44" ht="82.2" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Drafter's note (internal, delete before publishing): built as a Reference Matrix, matching the Data Retention Schedule (recast from Schedule to Reference Matrix). Header classification held at Internal per that precedent, even though the IDACS / CJIS row references CJIS and 240 IAC 5 retention; raise the classification if the agency treats this schedule itself as CJIS-controlled. Agency-supplied values left in brackets: [Agency Name], owner role, version and dates, and every retention period.</t>
@@ -994,8 +994,14 @@
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B18:B23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Classification" prompt="Select a value" type="list">
+      <formula1>"Internal,Restricted,Restricted / CJIS,Confidential"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1021,14 +1027,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="43.5" customHeight="1">
+    <row r="2" ht="50.5" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>How to use this template: replace every [BRACKETED] field with your agency's information and follow the « » guidance notes, then delete every « » note before publishing. This sheet explains each column; it is guidance only and can be removed once the record is populated.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, notes, review schedule and revision history live on the Matrix tab.</t>
@@ -1064,7 +1070,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Corner cell</t>
@@ -1130,7 +1136,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Cells</t>
@@ -1238,6 +1244,6 @@
     <mergeCell ref="B16:D16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>